--- a/results/网络拟合情况.xlsx
+++ b/results/网络拟合情况.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\神经网络训练\underwater_robot_control\results\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9E229A-49C4-4805-93BA-5E8CBB244F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,8 +26,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -29,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
   <si>
     <r>
       <rPr>
@@ -84,7 +88,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>epoch</t>
     </r>
@@ -141,7 +145,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>0112</t>
     </r>
@@ -161,7 +165,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>0331</t>
     </r>
@@ -184,7 +188,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>6</t>
     </r>
@@ -202,7 +206,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>RMSE</t>
     </r>
@@ -211,9 +215,6 @@
     <t>[0.064,0.076,0.095,0.429,0.349,0.873]</t>
   </si>
   <si>
-    <t>[0.137,0.158,0.093,1.650,1.250,2.471]</t>
-  </si>
-  <si>
     <t>[0.1641 0.1765 0.1622 0.263  0.2072 0.1908]</t>
   </si>
   <si>
@@ -229,15 +230,12 @@
     <t>[0.2721 0.2504 0.1292 0.1931 0.1913 0.223 ]</t>
   </si>
   <si>
-    <t>[0.0873 0.1311 0.1041 0.695  1.6275 1.1458]</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>6</t>
     </r>
@@ -255,7 +253,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>MAE</t>
     </r>
@@ -276,23 +274,39 @@
     <t>[0.1346 0.1094 0.0681 0.1113 0.1088 0.1243]</t>
   </si>
   <si>
-    <t>[0.0625 0.0888 0.0707 0.3176 0.3753 0.4385]</t>
-  </si>
-  <si>
     <t>Overall RMSE</t>
+  </si>
+  <si>
+    <t>理论公式计算</t>
+  </si>
+  <si>
+    <t>[6.159,2.272,15.263,5.468,3.493,12.923]</t>
+  </si>
+  <si>
+    <t>[5.078,1.736,10.181,3.958,2.555,9.878]</t>
+  </si>
+  <si>
+    <t>[0.0827 0.0557 0.0579 0.5055 1.0066 1.7802]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0.0515 0.0391 0.0401 0.2794 0.4272 0.78  ]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0.149, 0.161, 0.115, 1.23, 1.19, 2.544]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0.104, 0.114, 0.080, 0.289, 0.279, 0.480]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -304,7 +318,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -313,345 +327,22 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -659,251 +350,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -920,65 +369,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1228,24 +633,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="22.625" customWidth="1"/>
-    <col min="2" max="3" width="30.625" customWidth="1"/>
+    <col min="2" max="2" width="30.625" customWidth="1"/>
+    <col min="3" max="3" width="37.25" customWidth="1"/>
     <col min="4" max="4" width="35.875" customWidth="1"/>
     <col min="5" max="6" width="36.625" customWidth="1"/>
     <col min="7" max="7" width="37.125" customWidth="1"/>
     <col min="8" max="9" width="36.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:9">
+    <row r="1" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1262,7 +668,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" ht="15" spans="1:9">
+    <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1279,7 +685,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" ht="15" spans="1:9">
+    <row r="3" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1296,7 +702,7 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
-    <row r="4" ht="15" spans="1:9">
+    <row r="4" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -1312,7 +718,7 @@
       <c r="G4" s="1"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" ht="15" spans="1:9">
+    <row r="5" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1341,7 +747,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" ht="15" spans="1:9">
+    <row r="6" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -1370,32 +776,32 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" ht="15" spans="1:9">
+    <row r="7" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="1">
-        <v>0.03816</v>
+        <v>3.8159999999999999E-2</v>
       </c>
       <c r="C7" s="1">
-        <v>0.35129</v>
+        <v>0.35128999999999999</v>
       </c>
       <c r="D7" s="1">
         <v>20.352978</v>
       </c>
       <c r="E7" s="1">
-        <v>64.840663</v>
+        <v>64.840663000000006</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1">
-        <v>0.224212</v>
+        <v>0.22421199999999999</v>
       </c>
       <c r="I7" s="1">
-        <v>64.391266</v>
-      </c>
-    </row>
-    <row r="8" ht="15" spans="1:9">
+        <v>64.391266000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -1403,125 +809,152 @@
         <v>17</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15" x14ac:dyDescent="0.15">
+      <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" ht="15" spans="1:9">
-      <c r="A9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="H9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="I9" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15" x14ac:dyDescent="0.15">
+      <c r="A10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" ht="15" spans="1:9">
-      <c r="A10" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="B10" s="1">
-        <v>0.195346</v>
+        <v>0.19534599999999999</v>
       </c>
       <c r="C10" s="1">
-        <v>0.592698</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0.197018325328826</v>
-      </c>
-      <c r="E10" s="4">
+        <v>1.577421</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.19701832532882599</v>
+      </c>
+      <c r="E10" s="1">
         <v>1.45698654651641</v>
       </c>
-      <c r="F10" s="4">
-        <v>1.45084762573242</v>
-      </c>
-      <c r="G10" s="4">
-        <v>3.53402996063232</v>
-      </c>
-      <c r="H10" s="4">
-        <v>0.214877426624298</v>
-      </c>
-      <c r="I10" s="4">
-        <v>0.864129424095153</v>
-      </c>
-    </row>
-    <row r="12" ht="15" spans="1:3">
+      <c r="F10" s="1">
+        <v>1.4508476257324201</v>
+      </c>
+      <c r="G10" s="1">
+        <v>3.5340299606323202</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0.21487742662429801</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0.86132311820983798</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" ht="15" spans="2:3">
+    <row r="13" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" ht="15" spans="2:3">
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-    </row>
-    <row r="15" ht="15" spans="2:3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="C14" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15" x14ac:dyDescent="0.15">
+      <c r="A15" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
+      <c r="C15" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15" x14ac:dyDescent="0.15">
+      <c r="A16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15" x14ac:dyDescent="0.15">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.15">
+      <c r="A18" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/results/网络拟合情况.xlsx
+++ b/results/网络拟合情况.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\神经网络训练\underwater_robot_control\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9E229A-49C4-4805-93BA-5E8CBB244F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF6CD44-C0A8-40BE-A4BB-3D81D03D4D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="40">
   <si>
     <r>
       <rPr>
@@ -280,25 +280,57 @@
     <t>理论公式计算</t>
   </si>
   <si>
-    <t>[6.159,2.272,15.263,5.468,3.493,12.923]</t>
-  </si>
-  <si>
-    <t>[5.078,1.736,10.181,3.958,2.555,9.878]</t>
-  </si>
-  <si>
-    <t>[0.0827 0.0557 0.0579 0.5055 1.0066 1.7802]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>[0.0515 0.0391 0.0401 0.2794 0.4272 0.78  ]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>[0.149, 0.161, 0.115, 1.23, 1.19, 2.544]</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>[0.104, 0.114, 0.080, 0.289, 0.279, 0.480]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0.0967 0.0937 0.0989 0.8319 0.8997 1.1998]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0.0663 0.0617 0.0697 0.4029 0.4391 0.5529]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>[6.159,2.272,15.263,319.604,196.568,229.957]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>[5.078,1.736,10.181,231.985,141.130,153.825]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>纯</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>LSTM</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0.0381 0.0599 0.0955 0.1129 0.1343 0.1119]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0.0298 0.0534 0.0669 0.0835 0.0973 0.1006]</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -306,7 +338,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -332,6 +364,13 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -649,6 +688,7 @@
     <col min="5" max="6" width="36.625" customWidth="1"/>
     <col min="7" max="7" width="37.125" customWidth="1"/>
     <col min="8" max="9" width="36.625" customWidth="1"/>
+    <col min="10" max="10" width="21.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" x14ac:dyDescent="0.15">
@@ -809,7 +849,7 @@
         <v>17</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>18</v>
@@ -836,7 +876,7 @@
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>24</v>
@@ -883,7 +923,7 @@
         <v>0.21487742662429801</v>
       </c>
       <c r="I10" s="1">
-        <v>0.86132311820983798</v>
+        <v>0.70343935489654497</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" x14ac:dyDescent="0.15">
@@ -895,9 +935,15 @@
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="C14" s="4" t="s">
         <v>30</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15" x14ac:dyDescent="0.15">
@@ -908,32 +954,56 @@
       <c r="C15" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="D15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="16" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="15" x14ac:dyDescent="0.15">
+        <v>35</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.15">
+        <v>36</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
         <v>29</v>
+      </c>
+      <c r="D18" s="1">
+        <v>9.7869540000000005E-2</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0.70343935489654497</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
